--- a/GameConfig/Datas/道具/道具配置表.xlsx
+++ b/GameConfig/Datas/道具/道具配置表.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\道具\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B3117A-9AE6-4859-A89F-D287DDB76A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="道具配置表" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,114 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Jun</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">ps:
+0. 普通
+1. 材料
+2. 消耗品
+3. 展示用物品
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>ItemNameID</t>
+  </si>
+  <si>
+    <t>##道具名称</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>IconName_Man</t>
+  </si>
+  <si>
+    <t>IconName_Woman</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>FuncDescID</t>
+  </si>
+  <si>
+    <t>##功能描述</t>
+  </si>
+  <si>
+    <t>MaxStack</t>
+  </si>
+  <si>
+    <t>UseLevel</t>
+  </si>
+  <si>
+    <t>FuncType</t>
+  </si>
+  <si>
+    <t>FuncValue</t>
+  </si>
+  <si>
+    <t>DecomposeMoneyType</t>
+  </si>
+  <si>
+    <t>DecomposeMoneyCnt</t>
+  </si>
+  <si>
+    <t>DecomposeItemID</t>
+  </si>
+  <si>
+    <t>DecomposeItemCnt</t>
+  </si>
+  <si>
+    <t>GetDescID</t>
+  </si>
+  <si>
+    <t>##获得说明</t>
+  </si>
+  <si>
+    <t>AutoUse</t>
+  </si>
+  <si>
+    <t>ActiveFashionID</t>
+  </si>
+  <si>
+    <t>CanSell</t>
+  </si>
+  <si>
+    <t>CanCompose</t>
+  </si>
+  <si>
+    <t>GetWayID</t>
+  </si>
+  <si>
+    <t>JumpWayID</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -48,96 +144,21 @@
     <t>string</t>
   </si>
   <si>
+    <t>ColorQuality</t>
+  </si>
+  <si>
+    <t>list,int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>ItemID</t>
-  </si>
-  <si>
-    <t>ItemNameId</t>
-  </si>
-  <si>
-    <t>##道具名称</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>IconName_Man</t>
-  </si>
-  <si>
-    <t>IconName_Woman</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>FuncDescId</t>
-  </si>
-  <si>
-    <t>##功能描述</t>
-  </si>
-  <si>
-    <t>MaxStack</t>
-  </si>
-  <si>
-    <t>UseLevel</t>
-  </si>
-  <si>
-    <t>FuncType</t>
-  </si>
-  <si>
-    <t>FuncValue</t>
-  </si>
-  <si>
-    <t>DecomposeMoneyType</t>
-  </si>
-  <si>
-    <t>DecomposeMoneyCnt</t>
-  </si>
-  <si>
-    <t>DecomposeItemID</t>
-  </si>
-  <si>
-    <t>DecomposeItemCnt</t>
-  </si>
-  <si>
-    <t>GetDescId</t>
-  </si>
-  <si>
-    <t>##获得说明</t>
-  </si>
-  <si>
-    <t>AutoUse</t>
-  </si>
-  <si>
-    <t>ActiveFashionID</t>
-  </si>
-  <si>
-    <t>CanSell</t>
-  </si>
-  <si>
-    <t>CanCompose</t>
-  </si>
-  <si>
-    <t>GetWayID</t>
-  </si>
-  <si>
-    <t>JumpWayID</t>
-  </si>
-  <si>
-    <t>ColorQuality</t>
-  </si>
-  <si>
-    <t>list,int</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>道具ID</t>
   </si>
   <si>
@@ -213,6 +234,30 @@
     <t>使用跳转</t>
   </si>
   <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>基础货币，用途很广，在很多地方需要用到。</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>价值连城，比金币有着更大的购买力！</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>挑战关卡或者快速游历时消耗。</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>累计经验提升主角等级</t>
+  </si>
+  <si>
     <t>发型</t>
   </si>
   <si>
@@ -264,13 +309,13 @@
     <t>礼包</t>
   </si>
   <si>
-    <t>WayId</t>
-  </si>
-  <si>
-    <t>FuncId</t>
-  </si>
-  <si>
-    <t>ActivityId</t>
+    <t>WayID</t>
+  </si>
+  <si>
+    <t>FuncID</t>
+  </si>
+  <si>
+    <t>ActivityID</t>
   </si>
   <si>
     <t>WayName</t>
@@ -309,8 +354,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,7 +373,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -330,25 +380,146 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,12 +540,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -397,68 +742,352 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -716,116 +1345,116 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AE18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.4140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="22.5" style="13" customWidth="1"/>
+    <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="12.4166666666667" style="5" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="5" customWidth="1"/>
     <col min="5" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="18.75" style="13" customWidth="1"/>
+    <col min="10" max="10" width="39.0333333333333" style="5" customWidth="1"/>
     <col min="11" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="14" width="18.75" style="3" customWidth="1"/>
-    <col min="15" max="15" width="28" style="3" customWidth="1"/>
-    <col min="16" max="16" width="23.4140625" customWidth="1"/>
-    <col min="17" max="17" width="22.1640625" customWidth="1"/>
+    <col min="13" max="14" width="18.75" style="6" customWidth="1"/>
+    <col min="15" max="15" width="28" style="6" customWidth="1"/>
+    <col min="16" max="16" width="23.4166666666667" customWidth="1"/>
+    <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
     <col min="18" max="18" width="23.75" customWidth="1"/>
-    <col min="19" max="19" width="18.9140625" customWidth="1"/>
-    <col min="20" max="20" width="20.5" style="13" customWidth="1"/>
+    <col min="19" max="19" width="18.9166666666667" customWidth="1"/>
+    <col min="20" max="20" width="20.5" style="5" customWidth="1"/>
     <col min="21" max="21" width="21.75" customWidth="1"/>
     <col min="22" max="22" width="21.25" customWidth="1"/>
     <col min="23" max="23" width="26.25" customWidth="1"/>
-    <col min="24" max="24" width="23.1640625" customWidth="1"/>
+    <col min="24" max="24" width="23.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="20.75" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:31">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="AA1"/>
       <c r="AB1"/>
@@ -833,78 +1462,78 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
+    <row r="2" s="4" customFormat="1" spans="1:31">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D2" s="10"/>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="10"/>
+      <c r="U2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="10"/>
-      <c r="U2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>2</v>
+      <c r="V2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="AA2"/>
       <c r="AB2"/>
@@ -912,118 +1541,118 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+    <row r="3" s="4" customFormat="1" spans="1:31">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
       <c r="T3" s="10"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" s="3" customFormat="1" spans="1:31">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AA4"/>
@@ -1032,37 +1661,49 @@
       <c r="AD4"/>
       <c r="AE4"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="7">
-        <v>10300001</v>
-      </c>
-      <c r="D5" s="11" t="s">
+    <row r="5" customFormat="1" spans="1:31">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="11">
+        <v>40000001</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="13">
+        <v>3</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
+        <v>3</v>
+      </c>
+      <c r="I5" s="11">
+        <v>41000001</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="7">
-        <v>999</v>
-      </c>
-      <c r="L5" s="7">
+      <c r="K5" s="11">
+        <v>99999</v>
+      </c>
+      <c r="L5" s="11">
         <v>1</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5" s="5"/>
       <c r="U5" t="b">
         <v>0</v>
       </c>
+      <c r="V5"/>
       <c r="W5" t="b">
         <v>0</v>
       </c>
@@ -1070,37 +1711,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7">
-        <v>10001</v>
-      </c>
-      <c r="C6" s="7">
-        <v>10300002</v>
-      </c>
-      <c r="D6" s="11" t="s">
+    <row r="6" customFormat="1" spans="1:31">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="11">
+        <v>40000002</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="13">
+        <v>5</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11">
+        <v>3</v>
+      </c>
+      <c r="I6" s="11">
+        <v>41000002</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="7">
-        <v>999</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="K6" s="11">
+        <v>99999</v>
+      </c>
+      <c r="L6" s="11">
         <v>1</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6" s="5"/>
       <c r="U6" t="b">
         <v>0</v>
       </c>
+      <c r="V6"/>
       <c r="W6" t="b">
         <v>0</v>
       </c>
@@ -1108,37 +1761,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7">
-        <v>10002</v>
-      </c>
-      <c r="C7" s="7">
-        <v>10300003</v>
-      </c>
-      <c r="D7" s="11" t="s">
+    <row r="7" customFormat="1" spans="1:31">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="11">
+        <v>40000003</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="13">
+        <v>3</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11">
+        <v>3</v>
+      </c>
+      <c r="I7" s="11">
+        <v>41000003</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="7">
-        <v>999</v>
-      </c>
-      <c r="L7" s="7">
+      <c r="K7" s="11">
+        <v>99999</v>
+      </c>
+      <c r="L7" s="11">
         <v>1</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7" s="5"/>
       <c r="U7" t="b">
         <v>0</v>
       </c>
+      <c r="V7"/>
       <c r="W7" t="b">
         <v>0</v>
       </c>
@@ -1146,373 +1811,539 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7">
-        <v>10003</v>
-      </c>
-      <c r="C8" s="7">
-        <v>10300004</v>
+    <row r="8" customFormat="1" spans="1:31">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="11">
+        <v>40000004</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="13">
+        <v>4</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11">
+        <v>3</v>
+      </c>
+      <c r="I8" s="11">
+        <v>41000004</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="7">
+      <c r="K8" s="11">
+        <v>99999</v>
+      </c>
+      <c r="L8" s="11">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8" s="5"/>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8"/>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="11">
+        <v>40000005</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="11">
         <v>999</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L9" s="11">
         <v>1</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" t="b">
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7">
+    <row r="10" spans="1:31">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11">
+        <v>10001</v>
+      </c>
+      <c r="C10" s="11">
+        <v>40000006</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="11">
+        <v>999</v>
+      </c>
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11">
+        <v>10002</v>
+      </c>
+      <c r="C11" s="11">
+        <v>40000007</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="11">
+        <v>999</v>
+      </c>
+      <c r="L11" s="11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11">
+        <v>10003</v>
+      </c>
+      <c r="C12" s="11">
+        <v>40000008</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="11">
+        <v>999</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11">
         <v>10004</v>
       </c>
-      <c r="C9" s="7">
-        <v>10300005</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="7">
+      <c r="C13" s="11">
+        <v>40000009</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="11">
         <v>999</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L13" s="11">
         <v>1</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9" t="b">
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7">
+    <row r="14" spans="1:31">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11">
         <v>10005</v>
       </c>
-      <c r="C10" s="7">
-        <v>10300006</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="7">
+      <c r="C14" s="11">
+        <v>40000010</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="11">
         <v>999</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L14" s="11">
         <v>1</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10" t="b">
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7">
+    <row r="15" spans="1:31">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11">
         <v>10006</v>
       </c>
-      <c r="C11" s="7">
-        <v>10300007</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="7">
+      <c r="C15" s="11">
+        <v>40000011</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="11">
         <v>999</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L15" s="11">
         <v>1</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="U11" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" t="b">
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7">
+    <row r="16" spans="1:31">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11">
         <v>10007</v>
       </c>
-      <c r="C12" s="7">
-        <v>10300008</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="7">
+      <c r="C16" s="11">
+        <v>40000012</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="11">
         <v>999</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L16" s="11">
         <v>1</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="U12" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
-      </c>
-      <c r="X12" t="b">
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7">
+    <row r="17" spans="1:24">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11">
         <v>10008</v>
       </c>
-      <c r="C13" s="7">
-        <v>10300009</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="7">
+      <c r="C17" s="11">
+        <v>40000013</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="11">
         <v>999</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L17" s="11">
         <v>1</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="U13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13" t="b">
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7">
+    <row r="18" spans="1:24">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11">
         <v>10009</v>
       </c>
-      <c r="C14" s="7">
-        <v>10300010</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="7">
+      <c r="C18" s="11">
+        <v>40000014</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="11">
         <v>999</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L18" s="11">
         <v>1</v>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="U14" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" t="b">
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C7D26D1-7AB4-480D-8088-6B3FDAAE7C1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="17.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="23.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>81</v>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>83</v>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>89</v>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/道具/道具配置表.xlsx
+++ b/GameConfig/Datas/道具/道具配置表.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="道具配置表" sheetId="1" r:id="rId1"/>
-    <sheet name="获取途径配置表" sheetId="2" r:id="rId2"/>
+    <sheet name="货币配置表" sheetId="3" r:id="rId2"/>
+    <sheet name="获取途径配置表" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="117">
   <si>
     <t>##var</t>
   </si>
@@ -307,6 +308,63 @@
   </si>
   <si>
     <t>礼包</t>
+  </si>
+  <si>
+    <t>CurrencyType</t>
+  </si>
+  <si>
+    <t>BootyType</t>
+  </si>
+  <si>
+    <t>##货币名称</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>NotEnoughTextID</t>
+  </si>
+  <si>
+    <t>##货币不足提示文本</t>
+  </si>
+  <si>
+    <t>DescTextID</t>
+  </si>
+  <si>
+    <t>##描述文本</t>
+  </si>
+  <si>
+    <t>货币类型</t>
+  </si>
+  <si>
+    <t>掉落类型</t>
+  </si>
+  <si>
+    <t>货币名称</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>对应道具ID</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>货币不足提示文本ID</t>
+  </si>
+  <si>
+    <t>货币不足提示文本</t>
+  </si>
+  <si>
+    <t>描述文本ID</t>
+  </si>
+  <si>
+    <t>描述文本</t>
+  </si>
+  <si>
+    <t>货币不足！</t>
   </si>
   <si>
     <t>WayID</t>
@@ -540,13 +598,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -981,43 +1039,53 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1026,10 +1094,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1356,19 +1424,19 @@
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="12.4166666666667" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.4166666666667" style="12" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="12" customWidth="1"/>
     <col min="5" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="39.0333333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="39.0333333333333" style="12" customWidth="1"/>
     <col min="11" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="14" width="18.75" style="6" customWidth="1"/>
-    <col min="15" max="15" width="28" style="6" customWidth="1"/>
+    <col min="13" max="14" width="18.75" style="13" customWidth="1"/>
+    <col min="15" max="15" width="28" style="13" customWidth="1"/>
     <col min="16" max="16" width="23.4166666666667" customWidth="1"/>
     <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
     <col min="18" max="18" width="23.75" customWidth="1"/>
     <col min="19" max="19" width="18.9166666666667" customWidth="1"/>
-    <col min="20" max="20" width="20.5" style="5" customWidth="1"/>
+    <col min="20" max="20" width="20.5" style="12" customWidth="1"/>
     <col min="21" max="21" width="21.75" customWidth="1"/>
     <col min="22" max="22" width="21.25" customWidth="1"/>
     <col min="23" max="23" width="26.25" customWidth="1"/>
@@ -1377,83 +1445,83 @@
     <col min="26" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:31">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" s="10" customFormat="1" spans="1:31">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AA1"/>
@@ -1462,77 +1530,77 @@
       <c r="AD1"/>
       <c r="AE1"/>
     </row>
-    <row r="2" s="4" customFormat="1" spans="1:31">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="11" customFormat="1" spans="1:31">
+      <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="16"/>
+      <c r="K2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="10"/>
-      <c r="U2" s="2" t="s">
+      <c r="T2" s="16"/>
+      <c r="U2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AA2"/>
@@ -1541,118 +1609,118 @@
       <c r="AD2"/>
       <c r="AE2"/>
     </row>
-    <row r="3" s="4" customFormat="1" spans="1:31">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="11" customFormat="1" spans="1:31">
+      <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3"/>
       <c r="AE3"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:31">
-      <c r="A4" s="1" t="s">
+    <row r="4" s="10" customFormat="1" spans="1:31">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="T4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="X4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Z4" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AA4"/>
@@ -1662,44 +1730,44 @@
       <c r="AE4"/>
     </row>
     <row r="5" customFormat="1" spans="1:31">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1001</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="1">
         <v>40000001</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="17">
         <v>3</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11">
+      <c r="F5" s="18"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="1">
         <v>41000001</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="1">
         <v>99999</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5"/>
-      <c r="T5" s="5"/>
+      <c r="T5" s="12"/>
       <c r="U5" t="b">
         <v>0</v>
       </c>
@@ -1712,44 +1780,44 @@
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:31">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>1002</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="1">
         <v>40000002</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="17">
         <v>5</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11">
+      <c r="F6" s="18"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="1">
         <v>41000002</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="1">
         <v>99999</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6"/>
-      <c r="T6" s="5"/>
+      <c r="T6" s="12"/>
       <c r="U6" t="b">
         <v>0</v>
       </c>
@@ -1762,44 +1830,44 @@
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:31">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>1003</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="1">
         <v>40000003</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="17">
         <v>3</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11">
+      <c r="F7" s="18"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="1">
         <v>41000003</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="1">
         <v>99999</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7"/>
-      <c r="T7" s="5"/>
+      <c r="T7" s="12"/>
       <c r="U7" t="b">
         <v>0</v>
       </c>
@@ -1812,44 +1880,44 @@
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:31">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>1004</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="1">
         <v>40000004</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="17">
         <v>4</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>3</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="1">
         <v>41000004</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="1">
         <v>99999</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="1">
         <v>1</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
-      <c r="T8" s="5"/>
+      <c r="T8" s="12"/>
       <c r="U8" t="b">
         <v>0</v>
       </c>
@@ -1862,33 +1930,33 @@
       </c>
     </row>
     <row r="9" spans="1:31">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>1005</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="1">
         <v>40000005</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="11">
+      <c r="F9" s="18"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="1">
         <v>999</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="1">
         <v>1</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
       <c r="U9" t="b">
         <v>0</v>
       </c>
@@ -1900,33 +1968,33 @@
       </c>
     </row>
     <row r="10" spans="1:31">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
         <v>10001</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="1">
         <v>40000006</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="11">
+      <c r="F10" s="18"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="1">
         <v>999</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
       <c r="U10" t="b">
         <v>0</v>
       </c>
@@ -1938,33 +2006,33 @@
       </c>
     </row>
     <row r="11" spans="1:31">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
         <v>10002</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="1">
         <v>40000007</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="11">
+      <c r="F11" s="18"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="1">
         <v>999</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="1">
         <v>1</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
       <c r="U11" t="b">
         <v>0</v>
       </c>
@@ -1976,33 +2044,33 @@
       </c>
     </row>
     <row r="12" spans="1:31">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
         <v>10003</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="1">
         <v>40000008</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="11">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="1">
         <v>999</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="1">
         <v>1</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
       <c r="U12" t="b">
         <v>0</v>
       </c>
@@ -2014,33 +2082,33 @@
       </c>
     </row>
     <row r="13" spans="1:31">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
         <v>10004</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="1">
         <v>40000009</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="11">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="1">
         <v>999</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="1">
         <v>1</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="U13" t="b">
         <v>0</v>
       </c>
@@ -2052,33 +2120,33 @@
       </c>
     </row>
     <row r="14" spans="1:31">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
         <v>10005</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="1">
         <v>40000010</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="11">
+      <c r="F14" s="18"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="1">
         <v>999</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
       <c r="U14" t="b">
         <v>0</v>
       </c>
@@ -2090,33 +2158,33 @@
       </c>
     </row>
     <row r="15" spans="1:31">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
         <v>10006</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="1">
         <v>40000011</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="11">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="1">
         <v>999</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="1">
         <v>1</v>
       </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
       <c r="U15" t="b">
         <v>0</v>
       </c>
@@ -2128,33 +2196,33 @@
       </c>
     </row>
     <row r="16" spans="1:31">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
         <v>10007</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="1">
         <v>40000012</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="11">
+      <c r="F16" s="18"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="1">
         <v>999</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="1">
         <v>1</v>
       </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
       <c r="U16" t="b">
         <v>0</v>
       </c>
@@ -2166,33 +2234,33 @@
       </c>
     </row>
     <row r="17" spans="1:24">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
         <v>10008</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="1">
         <v>40000013</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="11">
+      <c r="F17" s="18"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="1">
         <v>999</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="1">
         <v>1</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
       <c r="U17" t="b">
         <v>0</v>
       </c>
@@ -2204,33 +2272,33 @@
       </c>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
         <v>10009</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="1">
         <v>40000014</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="11">
+      <c r="F18" s="18"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="1">
         <v>999</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="1">
         <v>1</v>
       </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
       <c r="U18" t="b">
         <v>0</v>
       </c>
@@ -2252,94 +2320,361 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <cols>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="24.125" customWidth="1"/>
+    <col min="5" max="5" width="32.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="24.75" customWidth="1"/>
+    <col min="8" max="8" width="25.5" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="20.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="21.25" customWidth="1"/>
+    <col min="12" max="12" width="50.5" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="7"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:12">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>40000001</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>11000002</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="1">
+        <v>41000001</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:12">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>40000002</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="I6" s="1">
+        <v>11000002</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="1">
+        <v>41000002</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:12">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="I7" s="1">
+        <v>11000002</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="1">
+        <v>41000003</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:12">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40000004</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1004</v>
+      </c>
+      <c r="I8" s="1">
+        <v>11000002</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="1">
+        <v>41000004</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="15.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="14.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="17.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="23.3333333333333" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>89</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>91</v>
+      <c r="F2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>97</v>
+      <c r="B4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/道具/道具配置表.xlsx
+++ b/GameConfig/Datas/道具/道具配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="道具配置表" sheetId="1" r:id="rId1"/>
@@ -2379,7 +2379,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>27</v>

--- a/GameConfig/Datas/道具/道具配置表.xlsx
+++ b/GameConfig/Datas/道具/道具配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="道具配置表" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,35 @@
     <author>Jun</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>ps:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+COLOR_NONE = 0; 无颜色
+COLOR_WHITE = 1; 白色
+COLOR_GREEN = 2; 绿色
+COLOR_BLUE = 3; 蓝色
+COLOR_PURPLE = 4; 紫色
+COLOR_ORANGE = 5; 橙色
+COLOR_RED = 6; 红色
+COLOR_CAI = 7; 彩色</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H1" authorId="0">
       <text>
         <r>
@@ -419,7 +448,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +601,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
